--- a/downloads/arbeitsdateien/04_Schule_1NF_zu_2NF.xlsx
+++ b/downloads/arbeitsdateien/04_Schule_1NF_zu_2NF.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER_UNTERRICHT_1NF" sheetId="1" r:id="R65877226e0a346c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER_UNTERRICHT_1NF" sheetId="1" r:id="R7af58c9324f54046"/>
   </x:sheets>
 </x:workbook>
 </file>
